--- a/database/excels/account/base-seeder.xlsx
+++ b/database/excels/account/base-seeder.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/monoland/Platform/monoland/database/excels/account/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2BD7C806-9198-5D42-BD6A-9890D4B03865}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4FF48048-BD2B-584A-99A4-2991EC9474FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2780" yWindow="1500" windowWidth="28040" windowHeight="17440" xr2:uid="{06FE2F46-4CD8-0043-8F7C-EC0B8906AE75}"/>
+    <workbookView xWindow="2780" yWindow="1500" windowWidth="28040" windowHeight="17440" activeTab="1" xr2:uid="{06FE2F46-4CD8-0043-8F7C-EC0B8906AE75}"/>
   </bookViews>
   <sheets>
     <sheet name="module" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="53">
   <si>
     <t>name</t>
   </si>
@@ -183,6 +183,12 @@
   </si>
   <si>
     <t>account</t>
+  </si>
+  <si>
+    <t>title</t>
+  </si>
+  <si>
+    <t>Pengaturan Profile</t>
   </si>
 </sst>
 </file>
@@ -618,19 +624,19 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2AE2BB2E-3CF2-A547-B570-E68310B07EC6}">
-  <dimension ref="A1:I5"/>
+  <dimension ref="A1:J5"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
-    <col min="3" max="3" width="21.83203125" customWidth="1"/>
-    <col min="4" max="4" width="17" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="17" customWidth="1"/>
-    <col min="6" max="6" width="35.5" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="10.83203125" style="3"/>
-    <col min="9" max="9" width="13.83203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="21.83203125" customWidth="1"/>
+    <col min="5" max="5" width="17" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="17" customWidth="1"/>
+    <col min="7" max="7" width="35.5" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="10.83203125" style="3"/>
+    <col min="10" max="10" width="13.83203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>10</v>
       </c>
@@ -638,54 +644,57 @@
         <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="H1" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="I1" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>41</v>
       </c>
       <c r="B2" t="s">
         <v>16</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>42</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>20</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>50</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
         <v>14</v>
       </c>
-      <c r="G2" s="3" t="b">
+      <c r="H2" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="H2" s="3" t="b">
+      <c r="I2" s="3" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>41</v>
       </c>
@@ -693,25 +702,28 @@
         <v>17</v>
       </c>
       <c r="C3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D3" t="s">
         <v>46</v>
       </c>
-      <c r="D3" t="s">
+      <c r="E3" t="s">
         <v>21</v>
       </c>
-      <c r="E3" t="s">
+      <c r="F3" t="s">
         <v>50</v>
       </c>
-      <c r="F3" t="s">
+      <c r="G3" t="s">
         <v>45</v>
       </c>
-      <c r="G3" s="3" t="b">
+      <c r="H3" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="H3" s="3" t="b">
+      <c r="I3" s="3" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>41</v>
       </c>
@@ -719,25 +731,28 @@
         <v>18</v>
       </c>
       <c r="C4" t="s">
+        <v>18</v>
+      </c>
+      <c r="D4" t="s">
         <v>43</v>
       </c>
-      <c r="D4" t="s">
+      <c r="E4" t="s">
         <v>22</v>
       </c>
-      <c r="E4" t="s">
+      <c r="F4" t="s">
         <v>50</v>
       </c>
-      <c r="F4" t="s">
+      <c r="G4" t="s">
         <v>25</v>
       </c>
-      <c r="G4" s="3" t="b">
+      <c r="H4" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="H4" s="3" t="b">
+      <c r="I4" s="3" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>41</v>
       </c>
@@ -745,21 +760,24 @@
         <v>47</v>
       </c>
       <c r="C5" t="s">
+        <v>52</v>
+      </c>
+      <c r="D5" t="s">
         <v>44</v>
       </c>
-      <c r="D5" t="s">
+      <c r="E5" t="s">
         <v>23</v>
       </c>
-      <c r="E5" t="s">
+      <c r="F5" t="s">
         <v>50</v>
       </c>
-      <c r="F5" t="s">
+      <c r="G5" t="s">
         <v>26</v>
       </c>
-      <c r="G5" s="3" t="b">
+      <c r="H5" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="H5" s="3" t="b">
+      <c r="I5" s="3" t="b">
         <v>0</v>
       </c>
     </row>
